--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -36,114 +36,114 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
-    <t xml:space="preserve">Villa Alemana</t>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
   </si>
   <si>
     <t xml:space="preserve">Limache</t>
   </si>
   <si>
-    <t xml:space="preserve">Quintero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Algarrobo</t>
+    <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
     <t xml:space="preserve">El Quisco</t>
   </si>
   <si>
-    <t xml:space="preserve">Concón</t>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
   </si>
   <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilpué</t>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Pascua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan Fernández</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
   </si>
   <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">Zapallar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panquehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Fernández</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,13 +580,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5605</v>
+        <v>5804</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5528</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="3">
@@ -597,13 +597,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5804</v>
+        <v>5103</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5527</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="4">
@@ -614,13 +614,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5802</v>
+        <v>5801</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4681</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5107</v>
+        <v>5605</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3761</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6">
@@ -648,13 +648,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5105</v>
+        <v>5602</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3686</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="7">
@@ -665,13 +665,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5602</v>
+        <v>5704</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3681</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="8">
@@ -682,13 +682,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>5604</v>
+        <v>5105</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3528</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="9">
@@ -699,13 +699,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5103</v>
+        <v>5606</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3366</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="10">
@@ -716,13 +716,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5603</v>
+        <v>5107</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2848</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="11">
@@ -733,13 +733,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5801</v>
+        <v>5102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2157</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="12">
@@ -750,13 +750,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5503</v>
+        <v>5802</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2024</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="13">
@@ -773,7 +773,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1996</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="14">
@@ -784,13 +784,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5401</v>
+        <v>5604</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1881</v>
+        <v>996</v>
       </c>
     </row>
     <row r="15">
@@ -801,13 +801,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5601</v>
+        <v>5501</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1791</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16">
@@ -818,13 +818,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5606</v>
+        <v>5601</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1767</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17">
@@ -835,13 +835,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5102</v>
+        <v>5504</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1767</v>
+        <v>898</v>
       </c>
     </row>
     <row r="18">
@@ -852,13 +852,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5504</v>
+        <v>5109</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1597</v>
+        <v>846</v>
       </c>
     </row>
     <row r="19">
@@ -869,13 +869,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5803</v>
+        <v>5301</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1301</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20">
@@ -886,13 +886,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5403</v>
+        <v>5303</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1289</v>
+        <v>683</v>
       </c>
     </row>
     <row r="21">
@@ -903,13 +903,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5302</v>
+        <v>5803</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>744</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22">
@@ -920,13 +920,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5705</v>
+        <v>5401</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>646</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23">
@@ -937,13 +937,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5702</v>
+        <v>5603</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>619</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24">
@@ -954,13 +954,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5303</v>
+        <v>5402</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>551</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25">
@@ -977,7 +977,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>539</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26">
@@ -988,13 +988,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5704</v>
+        <v>5403</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27">
@@ -1005,13 +1005,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5706</v>
+        <v>5506</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>333</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28">
@@ -1019,16 +1019,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5101</v>
+        <v>5706</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>273</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29">
@@ -1036,16 +1036,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5104</v>
+        <v>5702</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>33</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
@@ -1053,16 +1053,16 @@
         <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5506</v>
+        <v>5705</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>16</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31">
@@ -1070,16 +1070,16 @@
         <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5404</v>
+        <v>5201</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32">
@@ -1087,16 +1087,16 @@
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5201</v>
+        <v>5104</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-73</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="33">
@@ -1104,16 +1104,16 @@
         <v>5</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5402</v>
+        <v>5703</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-331</v>
+        <v>-131</v>
       </c>
     </row>
     <row r="34">
@@ -1121,16 +1121,16 @@
         <v>5</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5703</v>
+        <v>5302</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-749</v>
+        <v>-169</v>
       </c>
     </row>
     <row r="35">
@@ -1138,16 +1138,16 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5501</v>
+        <v>5404</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-752</v>
+        <v>-235</v>
       </c>
     </row>
     <row r="36">
@@ -1155,16 +1155,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5701</v>
+        <v>5503</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-1381</v>
+        <v>-324</v>
       </c>
     </row>
     <row r="37">
@@ -1172,16 +1172,16 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5109</v>
+        <v>5701</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-1430</v>
+        <v>-444</v>
       </c>
     </row>
     <row r="38">
@@ -1189,16 +1189,16 @@
         <v>5</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5301</v>
+        <v>5502</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-1641</v>
+        <v>-780</v>
       </c>
     </row>
     <row r="39">
@@ -1206,16 +1206,16 @@
         <v>5</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5502</v>
+        <v>5101</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-2582</v>
+        <v>-2831</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-04 08:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:08</t>
+    <t xml:space="preserve">2026-10-05 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
